--- a/NV Play NCU League and Saturday Cup player appearances for abandoned games.xlsx
+++ b/NV Play NCU League and Saturday Cup player appearances for abandoned games.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wylie\Downloads\Python Environment\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF7EAEC6-A96B-42D6-939B-D5F0D5864A13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24510" windowHeight="14280"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NV Play batting stats for seaso" sheetId="1" r:id="rId1"/>
@@ -1902,9 +1903,6 @@
     <t>Brian Anderson</t>
   </si>
   <si>
-    <t>Muhammad Asif</t>
-  </si>
-  <si>
     <t>Usman Ayub</t>
   </si>
   <si>
@@ -2035,12 +2033,15 @@
   </si>
   <si>
     <t>Surya Tummala</t>
+  </si>
+  <si>
+    <t>Mohammad Asif</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2518,9 +2519,8 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2841,8 +2841,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C4890"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C792"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="63.140625" customWidth="1"/>
@@ -5308,7 +5308,7 @@
         <v>624</v>
       </c>
       <c r="B224" t="s">
-        <v>627</v>
+        <v>671</v>
       </c>
       <c r="C224">
         <v>1</v>
@@ -5319,7 +5319,7 @@
         <v>624</v>
       </c>
       <c r="B225" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C225">
         <v>1</v>
@@ -5330,7 +5330,7 @@
         <v>624</v>
       </c>
       <c r="B226" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C226">
         <v>1</v>
@@ -5352,7 +5352,7 @@
         <v>624</v>
       </c>
       <c r="B228" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C228">
         <v>1</v>
@@ -5363,7 +5363,7 @@
         <v>624</v>
       </c>
       <c r="B229" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C229">
         <v>1</v>
@@ -5374,7 +5374,7 @@
         <v>624</v>
       </c>
       <c r="B230" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C230">
         <v>1</v>
@@ -5385,7 +5385,7 @@
         <v>624</v>
       </c>
       <c r="B231" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C231">
         <v>1</v>
@@ -5396,7 +5396,7 @@
         <v>624</v>
       </c>
       <c r="B232" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C232">
         <v>1</v>
@@ -5407,7 +5407,7 @@
         <v>624</v>
       </c>
       <c r="B233" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C233">
         <v>1</v>
@@ -5418,7 +5418,7 @@
         <v>624</v>
       </c>
       <c r="B234" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C234">
         <v>1</v>
@@ -5429,7 +5429,7 @@
         <v>624</v>
       </c>
       <c r="B235" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C235">
         <v>1</v>
@@ -5440,7 +5440,7 @@
         <v>624</v>
       </c>
       <c r="B236" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C236">
         <v>1</v>
@@ -5451,7 +5451,7 @@
         <v>624</v>
       </c>
       <c r="B237" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C237">
         <v>1</v>
@@ -5462,7 +5462,7 @@
         <v>624</v>
       </c>
       <c r="B238" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C238">
         <v>1</v>
@@ -5473,7 +5473,7 @@
         <v>624</v>
       </c>
       <c r="B239" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C239">
         <v>1</v>
@@ -5484,7 +5484,7 @@
         <v>624</v>
       </c>
       <c r="B240" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C240">
         <v>1</v>
@@ -5495,7 +5495,7 @@
         <v>624</v>
       </c>
       <c r="B241" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C241">
         <v>1</v>
@@ -5506,7 +5506,7 @@
         <v>624</v>
       </c>
       <c r="B242" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C242">
         <v>1</v>
@@ -5517,7 +5517,7 @@
         <v>624</v>
       </c>
       <c r="B243" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C243">
         <v>1</v>
@@ -5525,7 +5525,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B244" t="s">
         <v>434</v>
@@ -5536,7 +5536,7 @@
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B245" t="s">
         <v>435</v>
@@ -5547,10 +5547,10 @@
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
+        <v>645</v>
+      </c>
+      <c r="B246" t="s">
         <v>646</v>
-      </c>
-      <c r="B246" t="s">
-        <v>647</v>
       </c>
       <c r="C246">
         <v>1</v>
@@ -5558,7 +5558,7 @@
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B247" t="s">
         <v>277</v>
@@ -5569,7 +5569,7 @@
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B248" t="s">
         <v>437</v>
@@ -5580,7 +5580,7 @@
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B249" t="s">
         <v>278</v>
@@ -5591,7 +5591,7 @@
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B250" t="s">
         <v>438</v>
@@ -5602,7 +5602,7 @@
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B251" t="s">
         <v>279</v>
@@ -5613,10 +5613,10 @@
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B252" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C252">
         <v>1</v>
@@ -5624,10 +5624,10 @@
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B253" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C253">
         <v>1</v>
@@ -5635,7 +5635,7 @@
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B254" t="s">
         <v>439</v>
@@ -5646,7 +5646,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B255" t="s">
         <v>281</v>
@@ -5657,7 +5657,7 @@
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B256" t="s">
         <v>440</v>
@@ -5668,10 +5668,10 @@
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B257" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C257">
         <v>1</v>
@@ -5679,7 +5679,7 @@
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B258" t="s">
         <v>285</v>
@@ -5690,7 +5690,7 @@
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B259" t="s">
         <v>286</v>
@@ -5701,10 +5701,10 @@
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B260" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C260">
         <v>1</v>
@@ -5712,7 +5712,7 @@
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B261" t="s">
         <v>287</v>
@@ -5723,7 +5723,7 @@
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B262" t="s">
         <v>289</v>
@@ -5734,7 +5734,7 @@
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B263" t="s">
         <v>444</v>
@@ -5745,10 +5745,10 @@
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B264" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C264">
         <v>1</v>
@@ -5756,7 +5756,7 @@
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B265" t="s">
         <v>295</v>
@@ -5767,7 +5767,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B266" t="s">
         <v>186</v>
@@ -5778,7 +5778,7 @@
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B267" t="s">
         <v>189</v>
@@ -5789,7 +5789,7 @@
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B268" t="s">
         <v>190</v>
@@ -5800,10 +5800,10 @@
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
+        <v>652</v>
+      </c>
+      <c r="B269" t="s">
         <v>653</v>
-      </c>
-      <c r="B269" t="s">
-        <v>654</v>
       </c>
       <c r="C269">
         <v>1</v>
@@ -5811,10 +5811,10 @@
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B270" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C270">
         <v>1</v>
@@ -5822,10 +5822,10 @@
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B271" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C271">
         <v>1</v>
@@ -5833,10 +5833,10 @@
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B272" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C272">
         <v>1</v>
@@ -5844,7 +5844,7 @@
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B273" t="s">
         <v>201</v>
@@ -5855,10 +5855,10 @@
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B274" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C274">
         <v>1</v>
@@ -5866,10 +5866,10 @@
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B275" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C275">
         <v>1</v>
@@ -5877,10 +5877,10 @@
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B276" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="C276">
         <v>1</v>
@@ -5888,10 +5888,10 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B277" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C277">
         <v>1</v>
@@ -5899,10 +5899,10 @@
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B278" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C278">
         <v>1</v>
@@ -5910,10 +5910,10 @@
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B279" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C279">
         <v>1</v>
@@ -5921,10 +5921,10 @@
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B280" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C280">
         <v>1</v>
@@ -5932,10 +5932,10 @@
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B281" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C281">
         <v>1</v>
@@ -5943,10 +5943,10 @@
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B282" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C282">
         <v>1</v>
@@ -5954,10 +5954,10 @@
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B283" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C283">
         <v>1</v>
@@ -5965,10 +5965,10 @@
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B284" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C284">
         <v>1</v>
@@ -5976,10 +5976,10 @@
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B285" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="C285">
         <v>1</v>
@@ -5987,10 +5987,10 @@
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B286" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C286">
         <v>1</v>
@@ -5998,10 +5998,10 @@
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B287" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="C287">
         <v>1</v>
@@ -11561,102 +11561,6 @@
       <c r="C792">
         <v>1</v>
       </c>
-    </row>
-    <row r="4859" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4859" s="1"/>
-    </row>
-    <row r="4860" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4860" s="1"/>
-    </row>
-    <row r="4861" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4861" s="1"/>
-    </row>
-    <row r="4862" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4862" s="1"/>
-    </row>
-    <row r="4863" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4863" s="1"/>
-    </row>
-    <row r="4864" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4864" s="1"/>
-    </row>
-    <row r="4865" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4865" s="1"/>
-    </row>
-    <row r="4866" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4866" s="1"/>
-    </row>
-    <row r="4867" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4867" s="1"/>
-    </row>
-    <row r="4868" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4868" s="1"/>
-    </row>
-    <row r="4869" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4869" s="1"/>
-    </row>
-    <row r="4870" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4870" s="1"/>
-    </row>
-    <row r="4871" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4871" s="1"/>
-    </row>
-    <row r="4872" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4872" s="1"/>
-    </row>
-    <row r="4873" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4873" s="1"/>
-    </row>
-    <row r="4874" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4874" s="1"/>
-    </row>
-    <row r="4875" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4875" s="1"/>
-    </row>
-    <row r="4876" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4876" s="1"/>
-    </row>
-    <row r="4877" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4877" s="1"/>
-    </row>
-    <row r="4878" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4878" s="1"/>
-    </row>
-    <row r="4879" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4879" s="1"/>
-    </row>
-    <row r="4880" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4880" s="1"/>
-    </row>
-    <row r="4881" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4881" s="1"/>
-    </row>
-    <row r="4882" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4882" s="1"/>
-    </row>
-    <row r="4883" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4883" s="1"/>
-    </row>
-    <row r="4884" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4884" s="1"/>
-    </row>
-    <row r="4885" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4885" s="1"/>
-    </row>
-    <row r="4886" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4886" s="1"/>
-    </row>
-    <row r="4887" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4887" s="1"/>
-    </row>
-    <row r="4888" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4888" s="1"/>
-    </row>
-    <row r="4889" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4889" s="1"/>
-    </row>
-    <row r="4890" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4890" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/NV Play NCU League and Saturday Cup player appearances for abandoned games.xlsx
+++ b/NV Play NCU League and Saturday Cup player appearances for abandoned games.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wylie\Downloads\Python Environment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF7EAEC6-A96B-42D6-939B-D5F0D5864A13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3699B94-B1B1-4D68-B325-27A9B8738698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1585" uniqueCount="672">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1761" uniqueCount="717">
   <si>
     <t>Name</t>
   </si>
@@ -2036,6 +2036,141 @@
   </si>
   <si>
     <t>Mohammad Asif</t>
+  </si>
+  <si>
+    <t>Lisburn 2nd XI v CSNI 2nd XI, Wallace Park - 27 August 2026</t>
+  </si>
+  <si>
+    <t>Adam Berry</t>
+  </si>
+  <si>
+    <t>Ethan Booth</t>
+  </si>
+  <si>
+    <t>Luke Fisher</t>
+  </si>
+  <si>
+    <t>Chris Gault</t>
+  </si>
+  <si>
+    <t>Harshit Kokate</t>
+  </si>
+  <si>
+    <t>Stuart Lightbody</t>
+  </si>
+  <si>
+    <t>Pat Lutton</t>
+  </si>
+  <si>
+    <t>Mike McComish</t>
+  </si>
+  <si>
+    <t>Richard McConkey</t>
+  </si>
+  <si>
+    <t>Scott Mitchell</t>
+  </si>
+  <si>
+    <t>Tanish Sharma</t>
+  </si>
+  <si>
+    <t>Richard Simpson</t>
+  </si>
+  <si>
+    <t>Jonathan Waite</t>
+  </si>
+  <si>
+    <t>Harry Walker</t>
+  </si>
+  <si>
+    <t>Ian Whitten</t>
+  </si>
+  <si>
+    <t>CI 2nd XI v Woodvale 2nd XI, Belmont - 29 August 2026</t>
+  </si>
+  <si>
+    <t>Leo Bell</t>
+  </si>
+  <si>
+    <t>Patrick Charlton</t>
+  </si>
+  <si>
+    <t>Peter Harold</t>
+  </si>
+  <si>
+    <t>Syed Rameez Ali Hashmi</t>
+  </si>
+  <si>
+    <t>Adam Maitland</t>
+  </si>
+  <si>
+    <t>Chris Robinson</t>
+  </si>
+  <si>
+    <t>James Wright</t>
+  </si>
+  <si>
+    <t>Cregagh 2nd XI v BISC 2nd XI, Cregagh Memorial Recreation Ground - 29 August 2026</t>
+  </si>
+  <si>
+    <t>Christopher Baird</t>
+  </si>
+  <si>
+    <t>Thompson Dawson</t>
+  </si>
+  <si>
+    <t>Samuel  Grant</t>
+  </si>
+  <si>
+    <t>Indudhar Gurappa Jagadeesh</t>
+  </si>
+  <si>
+    <t>Sunil Lokhande</t>
+  </si>
+  <si>
+    <t>Mahendra Mande</t>
+  </si>
+  <si>
+    <t>Allen Mathew</t>
+  </si>
+  <si>
+    <t>Sudeep Sohan Misquith</t>
+  </si>
+  <si>
+    <t>Rory O'Hara</t>
+  </si>
+  <si>
+    <t>Chetan Pisal</t>
+  </si>
+  <si>
+    <t>Harry Stone</t>
+  </si>
+  <si>
+    <t>James Walker</t>
+  </si>
+  <si>
+    <t>Templepatrick 1st XI v Armagh 1st XI, The Cloughan - 29 August 2026</t>
+  </si>
+  <si>
+    <t>Connor Courtney</t>
+  </si>
+  <si>
+    <t>Ryan Hetherington</t>
+  </si>
+  <si>
+    <t>Oliver Mann</t>
+  </si>
+  <si>
+    <t>William Mann</t>
+  </si>
+  <si>
+    <t>Josh Stoops</t>
+  </si>
+  <si>
+    <t>Nick Van Der Linde</t>
+  </si>
+  <si>
+    <t>Matthew Wilson</t>
   </si>
 </sst>
 </file>
@@ -2842,7 +2977,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C792"/>
+  <dimension ref="A1:C880"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="63.140625" customWidth="1"/>
@@ -11562,6 +11697,974 @@
         <v>1</v>
       </c>
     </row>
+    <row r="793" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A793" t="s">
+        <v>672</v>
+      </c>
+      <c r="B793" t="s">
+        <v>673</v>
+      </c>
+      <c r="C793">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="794" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A794" t="s">
+        <v>672</v>
+      </c>
+      <c r="B794" t="s">
+        <v>674</v>
+      </c>
+      <c r="C794">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="795" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A795" t="s">
+        <v>672</v>
+      </c>
+      <c r="B795" t="s">
+        <v>523</v>
+      </c>
+      <c r="C795">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="796" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A796" t="s">
+        <v>672</v>
+      </c>
+      <c r="B796" t="s">
+        <v>675</v>
+      </c>
+      <c r="C796">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="797" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A797" t="s">
+        <v>672</v>
+      </c>
+      <c r="B797" t="s">
+        <v>676</v>
+      </c>
+      <c r="C797">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="798" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A798" t="s">
+        <v>672</v>
+      </c>
+      <c r="B798" t="s">
+        <v>527</v>
+      </c>
+      <c r="C798">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="799" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A799" t="s">
+        <v>672</v>
+      </c>
+      <c r="B799" t="s">
+        <v>528</v>
+      </c>
+      <c r="C799">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="800" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A800" t="s">
+        <v>672</v>
+      </c>
+      <c r="B800" t="s">
+        <v>529</v>
+      </c>
+      <c r="C800">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="801" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A801" t="s">
+        <v>672</v>
+      </c>
+      <c r="B801" t="s">
+        <v>332</v>
+      </c>
+      <c r="C801">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="802" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A802" t="s">
+        <v>672</v>
+      </c>
+      <c r="B802" t="s">
+        <v>677</v>
+      </c>
+      <c r="C802">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="803" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A803" t="s">
+        <v>672</v>
+      </c>
+      <c r="B803" t="s">
+        <v>678</v>
+      </c>
+      <c r="C803">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="804" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A804" t="s">
+        <v>672</v>
+      </c>
+      <c r="B804" t="s">
+        <v>679</v>
+      </c>
+      <c r="C804">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="805" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A805" t="s">
+        <v>672</v>
+      </c>
+      <c r="B805" t="s">
+        <v>680</v>
+      </c>
+      <c r="C805">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="806" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A806" t="s">
+        <v>672</v>
+      </c>
+      <c r="B806" t="s">
+        <v>681</v>
+      </c>
+      <c r="C806">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="807" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A807" t="s">
+        <v>672</v>
+      </c>
+      <c r="B807" t="s">
+        <v>62</v>
+      </c>
+      <c r="C807">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="808" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A808" t="s">
+        <v>672</v>
+      </c>
+      <c r="B808" t="s">
+        <v>682</v>
+      </c>
+      <c r="C808">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="809" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A809" t="s">
+        <v>672</v>
+      </c>
+      <c r="B809" t="s">
+        <v>683</v>
+      </c>
+      <c r="C809">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="810" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A810" t="s">
+        <v>672</v>
+      </c>
+      <c r="B810" t="s">
+        <v>684</v>
+      </c>
+      <c r="C810">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="811" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A811" t="s">
+        <v>672</v>
+      </c>
+      <c r="B811" t="s">
+        <v>685</v>
+      </c>
+      <c r="C811">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="812" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A812" t="s">
+        <v>672</v>
+      </c>
+      <c r="B812" t="s">
+        <v>686</v>
+      </c>
+      <c r="C812">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="813" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A813" t="s">
+        <v>672</v>
+      </c>
+      <c r="B813" t="s">
+        <v>66</v>
+      </c>
+      <c r="C813">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="814" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A814" t="s">
+        <v>672</v>
+      </c>
+      <c r="B814" t="s">
+        <v>687</v>
+      </c>
+      <c r="C814">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="815" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A815" t="s">
+        <v>688</v>
+      </c>
+      <c r="B815" t="s">
+        <v>349</v>
+      </c>
+      <c r="C815">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="816" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A816" t="s">
+        <v>688</v>
+      </c>
+      <c r="B816" t="s">
+        <v>689</v>
+      </c>
+      <c r="C816">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="817" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A817" t="s">
+        <v>688</v>
+      </c>
+      <c r="B817" t="s">
+        <v>166</v>
+      </c>
+      <c r="C817">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="818" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A818" t="s">
+        <v>688</v>
+      </c>
+      <c r="B818" t="s">
+        <v>583</v>
+      </c>
+      <c r="C818">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="819" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A819" t="s">
+        <v>688</v>
+      </c>
+      <c r="B819" t="s">
+        <v>518</v>
+      </c>
+      <c r="C819">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="820" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A820" t="s">
+        <v>688</v>
+      </c>
+      <c r="B820" t="s">
+        <v>690</v>
+      </c>
+      <c r="C820">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="821" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A821" t="s">
+        <v>688</v>
+      </c>
+      <c r="B821" t="s">
+        <v>521</v>
+      </c>
+      <c r="C821">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="822" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A822" t="s">
+        <v>688</v>
+      </c>
+      <c r="B822" t="s">
+        <v>524</v>
+      </c>
+      <c r="C822">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="823" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A823" t="s">
+        <v>688</v>
+      </c>
+      <c r="B823" t="s">
+        <v>525</v>
+      </c>
+      <c r="C823">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="824" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A824" t="s">
+        <v>688</v>
+      </c>
+      <c r="B824" t="s">
+        <v>330</v>
+      </c>
+      <c r="C824">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="825" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A825" t="s">
+        <v>688</v>
+      </c>
+      <c r="B825" t="s">
+        <v>691</v>
+      </c>
+      <c r="C825">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="826" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A826" t="s">
+        <v>688</v>
+      </c>
+      <c r="B826" t="s">
+        <v>692</v>
+      </c>
+      <c r="C826">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="827" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A827" t="s">
+        <v>688</v>
+      </c>
+      <c r="B827" t="s">
+        <v>482</v>
+      </c>
+      <c r="C827">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="828" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A828" t="s">
+        <v>688</v>
+      </c>
+      <c r="B828" t="s">
+        <v>693</v>
+      </c>
+      <c r="C828">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="829" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A829" t="s">
+        <v>688</v>
+      </c>
+      <c r="B829" t="s">
+        <v>588</v>
+      </c>
+      <c r="C829">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="830" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A830" t="s">
+        <v>688</v>
+      </c>
+      <c r="B830" t="s">
+        <v>360</v>
+      </c>
+      <c r="C830">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="831" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A831" t="s">
+        <v>688</v>
+      </c>
+      <c r="B831" t="s">
+        <v>336</v>
+      </c>
+      <c r="C831">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="832" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A832" t="s">
+        <v>688</v>
+      </c>
+      <c r="B832" t="s">
+        <v>694</v>
+      </c>
+      <c r="C832">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="833" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A833" t="s">
+        <v>688</v>
+      </c>
+      <c r="B833" t="s">
+        <v>533</v>
+      </c>
+      <c r="C833">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="834" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A834" t="s">
+        <v>688</v>
+      </c>
+      <c r="B834" t="s">
+        <v>590</v>
+      </c>
+      <c r="C834">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="835" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A835" t="s">
+        <v>688</v>
+      </c>
+      <c r="B835" t="s">
+        <v>364</v>
+      </c>
+      <c r="C835">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="836" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A836" t="s">
+        <v>688</v>
+      </c>
+      <c r="B836" t="s">
+        <v>695</v>
+      </c>
+      <c r="C836">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="837" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A837" t="s">
+        <v>696</v>
+      </c>
+      <c r="B837" t="s">
+        <v>697</v>
+      </c>
+      <c r="C837">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="838" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A838" t="s">
+        <v>696</v>
+      </c>
+      <c r="B838" t="s">
+        <v>393</v>
+      </c>
+      <c r="C838">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="839" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A839" t="s">
+        <v>696</v>
+      </c>
+      <c r="B839" t="s">
+        <v>698</v>
+      </c>
+      <c r="C839">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="840" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A840" t="s">
+        <v>696</v>
+      </c>
+      <c r="B840" t="s">
+        <v>396</v>
+      </c>
+      <c r="C840">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="841" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A841" t="s">
+        <v>696</v>
+      </c>
+      <c r="B841" t="s">
+        <v>74</v>
+      </c>
+      <c r="C841">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="842" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A842" t="s">
+        <v>696</v>
+      </c>
+      <c r="B842" t="s">
+        <v>699</v>
+      </c>
+      <c r="C842">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="843" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A843" t="s">
+        <v>696</v>
+      </c>
+      <c r="B843" t="s">
+        <v>401</v>
+      </c>
+      <c r="C843">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="844" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A844" t="s">
+        <v>696</v>
+      </c>
+      <c r="B844" t="s">
+        <v>700</v>
+      </c>
+      <c r="C844">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="845" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A845" t="s">
+        <v>696</v>
+      </c>
+      <c r="B845" t="s">
+        <v>78</v>
+      </c>
+      <c r="C845">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="846" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A846" t="s">
+        <v>696</v>
+      </c>
+      <c r="B846" t="s">
+        <v>79</v>
+      </c>
+      <c r="C846">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="847" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A847" t="s">
+        <v>696</v>
+      </c>
+      <c r="B847" t="s">
+        <v>701</v>
+      </c>
+      <c r="C847">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="848" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A848" t="s">
+        <v>696</v>
+      </c>
+      <c r="B848" t="s">
+        <v>702</v>
+      </c>
+      <c r="C848">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="849" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A849" t="s">
+        <v>696</v>
+      </c>
+      <c r="B849" t="s">
+        <v>703</v>
+      </c>
+      <c r="C849">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="850" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A850" t="s">
+        <v>696</v>
+      </c>
+      <c r="B850" t="s">
+        <v>704</v>
+      </c>
+      <c r="C850">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="851" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A851" t="s">
+        <v>696</v>
+      </c>
+      <c r="B851" t="s">
+        <v>85</v>
+      </c>
+      <c r="C851">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="852" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A852" t="s">
+        <v>696</v>
+      </c>
+      <c r="B852" t="s">
+        <v>705</v>
+      </c>
+      <c r="C852">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="853" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A853" t="s">
+        <v>696</v>
+      </c>
+      <c r="B853" t="s">
+        <v>179</v>
+      </c>
+      <c r="C853">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="854" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A854" t="s">
+        <v>696</v>
+      </c>
+      <c r="B854" t="s">
+        <v>706</v>
+      </c>
+      <c r="C854">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="855" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A855" t="s">
+        <v>696</v>
+      </c>
+      <c r="B855" t="s">
+        <v>89</v>
+      </c>
+      <c r="C855">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="856" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A856" t="s">
+        <v>696</v>
+      </c>
+      <c r="B856" t="s">
+        <v>183</v>
+      </c>
+      <c r="C856">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="857" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A857" t="s">
+        <v>696</v>
+      </c>
+      <c r="B857" t="s">
+        <v>707</v>
+      </c>
+      <c r="C857">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="858" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A858" t="s">
+        <v>696</v>
+      </c>
+      <c r="B858" t="s">
+        <v>708</v>
+      </c>
+      <c r="C858">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="859" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A859" t="s">
+        <v>709</v>
+      </c>
+      <c r="B859" t="s">
+        <v>433</v>
+      </c>
+      <c r="C859">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="860" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A860" t="s">
+        <v>709</v>
+      </c>
+      <c r="B860" t="s">
+        <v>710</v>
+      </c>
+      <c r="C860">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="861" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A861" t="s">
+        <v>709</v>
+      </c>
+      <c r="B861" t="s">
+        <v>570</v>
+      </c>
+      <c r="C861">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="862" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A862" t="s">
+        <v>709</v>
+      </c>
+      <c r="B862" t="s">
+        <v>437</v>
+      </c>
+      <c r="C862">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="863" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A863" t="s">
+        <v>709</v>
+      </c>
+      <c r="B863" t="s">
+        <v>438</v>
+      </c>
+      <c r="C863">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="864" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A864" t="s">
+        <v>709</v>
+      </c>
+      <c r="B864" t="s">
+        <v>711</v>
+      </c>
+      <c r="C864">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="865" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A865" t="s">
+        <v>709</v>
+      </c>
+      <c r="B865" t="s">
+        <v>648</v>
+      </c>
+      <c r="C865">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="866" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A866" t="s">
+        <v>709</v>
+      </c>
+      <c r="B866" t="s">
+        <v>571</v>
+      </c>
+      <c r="C866">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="867" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A867" t="s">
+        <v>709</v>
+      </c>
+      <c r="B867" t="s">
+        <v>712</v>
+      </c>
+      <c r="C867">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="868" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A868" t="s">
+        <v>709</v>
+      </c>
+      <c r="B868" t="s">
+        <v>713</v>
+      </c>
+      <c r="C868">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="869" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A869" t="s">
+        <v>709</v>
+      </c>
+      <c r="B869" t="s">
+        <v>573</v>
+      </c>
+      <c r="C869">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="870" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A870" t="s">
+        <v>709</v>
+      </c>
+      <c r="B870" t="s">
+        <v>649</v>
+      </c>
+      <c r="C870">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="871" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A871" t="s">
+        <v>709</v>
+      </c>
+      <c r="B871" t="s">
+        <v>650</v>
+      </c>
+      <c r="C871">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="872" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A872" t="s">
+        <v>709</v>
+      </c>
+      <c r="B872" t="s">
+        <v>575</v>
+      </c>
+      <c r="C872">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="873" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A873" t="s">
+        <v>709</v>
+      </c>
+      <c r="B873" t="s">
+        <v>442</v>
+      </c>
+      <c r="C873">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="874" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A874" t="s">
+        <v>709</v>
+      </c>
+      <c r="B874" t="s">
+        <v>443</v>
+      </c>
+      <c r="C874">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="875" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A875" t="s">
+        <v>709</v>
+      </c>
+      <c r="B875" t="s">
+        <v>714</v>
+      </c>
+      <c r="C875">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="876" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A876" t="s">
+        <v>709</v>
+      </c>
+      <c r="B876" t="s">
+        <v>444</v>
+      </c>
+      <c r="C876">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="877" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A877" t="s">
+        <v>709</v>
+      </c>
+      <c r="B877" t="s">
+        <v>715</v>
+      </c>
+      <c r="C877">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="878" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A878" t="s">
+        <v>709</v>
+      </c>
+      <c r="B878" t="s">
+        <v>716</v>
+      </c>
+      <c r="C878">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="879" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A879" t="s">
+        <v>709</v>
+      </c>
+      <c r="B879" t="s">
+        <v>577</v>
+      </c>
+      <c r="C879">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="880" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A880" t="s">
+        <v>709</v>
+      </c>
+      <c r="B880" t="s">
+        <v>578</v>
+      </c>
+      <c r="C880">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
